--- a/research/traditional_assets/database/data/france/france_shoe.xlsx
+++ b/research/traditional_assets/database/data/france/france_shoe.xlsx
@@ -587,23 +587,26 @@
           <t>Shoe</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.09359999999999999</v>
+      </c>
       <c r="G2">
-        <v>-0.1253731343283582</v>
+        <v>0.1931899641577061</v>
       </c>
       <c r="H2">
-        <v>-0.1253731343283582</v>
+        <v>0.1931899641577061</v>
       </c>
       <c r="I2">
-        <v>0.05522388059701492</v>
+        <v>0.1508960573476703</v>
       </c>
       <c r="J2">
-        <v>0.05522388059701492</v>
+        <v>0.1508960573476703</v>
       </c>
       <c r="K2">
-        <v>-0.032</v>
+        <v>0.228</v>
       </c>
       <c r="L2">
-        <v>-0.01194029850746269</v>
+        <v>0.08172043010752689</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,37 +624,37 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="V2">
-        <v>1.735159817351598</v>
+        <v>1.429657794676806</v>
       </c>
       <c r="W2">
-        <v>-0.007048458149779736</v>
+        <v>0.048</v>
       </c>
       <c r="X2">
-        <v>0.06582695625544722</v>
+        <v>0.1051606487081209</v>
       </c>
       <c r="Y2">
-        <v>-0.07287541440522696</v>
+        <v>-0.05716064870812088</v>
       </c>
       <c r="Z2">
-        <v>6.189376443418012</v>
+        <v>9.393939393939389</v>
       </c>
       <c r="AA2">
-        <v>0.3418013856812931</v>
+        <v>1.417508417508417</v>
       </c>
       <c r="AB2">
-        <v>0.06582695625544722</v>
+        <v>0.1051606487081209</v>
       </c>
       <c r="AC2">
-        <v>0.2759744294258459</v>
+        <v>1.312347768800296</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -663,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-3.8</v>
+        <v>-3.76</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -672,25 +675,22 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>2.360248447204969</v>
+        <v>3.327433628318584</v>
       </c>
       <c r="AK2">
-        <v>-3.999999999999999</v>
+        <v>-5.696969696969695</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-20.99447513812155</v>
-      </c>
-      <c r="AQ2">
-        <v>-148</v>
+        <v>-8.44943820224719</v>
       </c>
     </row>
     <row r="3">
@@ -709,23 +709,26 @@
           <t>Shoe</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.09359999999999999</v>
+      </c>
       <c r="G3">
-        <v>-0.1253731343283582</v>
+        <v>0.1931899641577061</v>
       </c>
       <c r="H3">
-        <v>-0.1253731343283582</v>
+        <v>0.1931899641577061</v>
       </c>
       <c r="I3">
-        <v>0.05522388059701492</v>
+        <v>0.1508960573476703</v>
       </c>
       <c r="J3">
-        <v>0.05522388059701492</v>
+        <v>0.1508960573476703</v>
       </c>
       <c r="K3">
-        <v>-0.032</v>
+        <v>0.228</v>
       </c>
       <c r="L3">
-        <v>-0.01194029850746269</v>
+        <v>0.08172043010752689</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -734,7 +737,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -743,37 +746,37 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="V3">
-        <v>1.735159817351598</v>
+        <v>1.429657794676806</v>
       </c>
       <c r="W3">
-        <v>-0.007048458149779736</v>
+        <v>0.048</v>
       </c>
       <c r="X3">
-        <v>0.06582695625544722</v>
+        <v>0.1051606487081209</v>
       </c>
       <c r="Y3">
-        <v>-0.07287541440522696</v>
+        <v>-0.05716064870812088</v>
       </c>
       <c r="Z3">
-        <v>6.189376443418012</v>
+        <v>9.393939393939389</v>
       </c>
       <c r="AA3">
-        <v>0.3418013856812931</v>
+        <v>1.417508417508417</v>
       </c>
       <c r="AB3">
-        <v>0.06582695625544722</v>
+        <v>0.1051606487081209</v>
       </c>
       <c r="AC3">
-        <v>0.2759744294258459</v>
+        <v>1.312347768800296</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -785,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-3.8</v>
+        <v>-3.76</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -794,25 +797,22 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>2.360248447204969</v>
+        <v>3.327433628318584</v>
       </c>
       <c r="AK3">
-        <v>-3.999999999999999</v>
+        <v>-5.696969696969695</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-20.99447513812155</v>
-      </c>
-      <c r="AQ3">
-        <v>-148</v>
+        <v>-8.44943820224719</v>
       </c>
     </row>
   </sheetData>
